--- a/main/data/schedule.xlsx
+++ b/main/data/schedule.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\project\energetic_site\main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92C376FB-1069-435C-B4E5-79C6E353F030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F0D2881-AC0D-461D-925C-84CEB3FE9533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Январь 2026" sheetId="1" r:id="rId1"/>
     <sheet name="Февраль 2026" sheetId="2" r:id="rId2"/>
     <sheet name="Март 2026" sheetId="3" r:id="rId3"/>
+    <sheet name="Апрель 2026" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="14">
   <si>
     <t>03.02.2026 — 14.02.2026</t>
   </si>
@@ -78,6 +79,9 @@
   </si>
   <si>
     <t>14.03.2026 — 17.03.2026</t>
+  </si>
+  <si>
+    <t>Формат - Дистанционный</t>
   </si>
 </sst>
 </file>
@@ -447,6 +451,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E995CB2D-0483-4159-8CFD-45A6D8D13217}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="102.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.88671875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -547,4 +555,60 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5526FC9-C698-47D0-99AD-2CAE6F6B4D6B}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/main/data/schedule.xlsx
+++ b/main/data/schedule.xlsx
@@ -8,15 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\project\energetic_site\main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F0D2881-AC0D-461D-925C-84CEB3FE9533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38A8D5C6-9EB0-4A3A-B10D-9570AF543F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Январь 2026" sheetId="1" r:id="rId1"/>
-    <sheet name="Февраль 2026" sheetId="2" r:id="rId2"/>
-    <sheet name="Март 2026" sheetId="3" r:id="rId3"/>
-    <sheet name="Апрель 2026" sheetId="4" r:id="rId4"/>
+    <sheet name="Апрель 2026" sheetId="4" r:id="rId1"/>
+    <sheet name="Май 2026" sheetId="5" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,16 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="14">
-  <si>
-    <t>03.02.2026 — 14.02.2026</t>
-  </si>
-  <si>
-    <t>Работы на высоте</t>
-  </si>
-  <si>
-    <t>ОЗП</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="37">
   <si>
     <t>Название</t>
   </si>
@@ -48,11 +37,131 @@
     <t>Форма</t>
   </si>
   <si>
-    <t>ПРОВЕРКА</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">02.02.-06.02.2026 </t>
+    <t>Формат - Дистанционный</t>
+  </si>
+  <si>
+    <t>Программа подготовки и проверки знаний работников 1,2,3 группы по охране труда при работе в ограниченных и замкнутых пространствах</t>
+  </si>
+  <si>
+    <t>Программа повышения квалификации для персонала, обслуживающего трубопроводы пара и горячей воды</t>
+  </si>
+  <si>
+    <t>Программа ПК электротехнического персонала (испытание оборудования повышенным напряжением)</t>
+  </si>
+  <si>
+    <t>Программа повышения квалификации  электротехнического персонала</t>
+  </si>
+  <si>
+    <t>Подготовка работников, занятых выполнением работ в электроустановках на группу допуска по электробезопасности</t>
+  </si>
+  <si>
+    <t>Программа обучения требованиям охраны труда (А, Б, В)</t>
+  </si>
+  <si>
+    <t>Программа обучения по оказанию первой  помощи пострадавшим</t>
+  </si>
+  <si>
+    <t>Программа обучения по использованию (применению) средств индивидуальной защиты</t>
+  </si>
+  <si>
+    <t>Программа повышения квалификации для рабочих люльки, находящихся на подъемнике (вышке)</t>
+  </si>
+  <si>
+    <t>Повышение квалификации в области пожарной безопасности</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">01.04.-07.04.2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(Теоретический курс в дистанционном формате 01.04.-03.04.26; Практика в УЦ и экзамен 06.04.-07.04.26)</t>
+    </r>
+  </si>
+  <si>
+    <t>06.04.-08.04.2026</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">15.04.-16.04.2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(Теоретический курс в дистанционном формате 15.04.26; Практика в УЦ и экзамен 16.04.26)</t>
+    </r>
+  </si>
+  <si>
+    <t>22.04.-24.04.2026</t>
+  </si>
+  <si>
+    <t>13.04.-23.04.2026</t>
+  </si>
+  <si>
+    <t>16.04.-22.04.2026</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">16.04.-17.04.2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(Теоретический курс в дистанционном формате 16.04.26; Практика в УЦ и экзамен 17.04.26)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">22.04.-24.04.2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(Теоретический курс в дистанционном формате 22.04.-23.04.26; Практика в УЦ и экзамен 24.04.26)</t>
+    </r>
+  </si>
+  <si>
+    <t>Формат - Дистанционно-очный</t>
+  </si>
+  <si>
+    <t>Формат - Очный</t>
+  </si>
+  <si>
+    <t>Программа повышения квалификации для рабочих, осуществляющих транспортировку, хранение и эксплуатацию баллонов со сжатыми, сжиженными и растворенными под давлением газами</t>
+  </si>
+  <si>
+    <t>Правила по охране труда при работе на высоте</t>
+  </si>
+  <si>
+    <t>Программа обучения по оказанию первой помощи пострадавшим</t>
+  </si>
+  <si>
+    <t>Программа повышения квалификации руководителей и специалистов опасных производственных объектов по промышленной безопасности</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">06.05.-13.05.2026 </t>
     </r>
     <r>
       <rPr>
@@ -62,46 +171,93 @@
         <family val="1"/>
         <charset val="204"/>
       </rPr>
-      <t>(Теоретический курс в дистанционном формате 02.02.-04.02.26; Практика в УЦ и экзамен 05.02.-06.02.26)</t>
-    </r>
-  </si>
-  <si>
-    <t>ПК по ПБ</t>
-  </si>
-  <si>
-    <t>Стропальщик</t>
-  </si>
-  <si>
-    <t>02.03.2026 — 06.03.2026</t>
-  </si>
-  <si>
-    <t>12.02.2026 — 01.04.2026</t>
-  </si>
-  <si>
-    <t>14.03.2026 — 17.03.2026</t>
-  </si>
-  <si>
-    <t>Формат - Дистанционный</t>
+      <t>(Теоретический курс в дистанционном формате 06.05.-08.05.26; Практика в УЦ и экзамен 12.05.-13.05.26)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">18.05.-22.05.2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(Теоретический курс в дистанционном формате 18.05.-20.05.26; Практика в УЦ и экзамен 21.05.-22.05.26)</t>
+    </r>
+  </si>
+  <si>
+    <t>20.05.-26.05.2026</t>
+  </si>
+  <si>
+    <t>12.05.-22.05.2026</t>
+  </si>
+  <si>
+    <t>13.05.-15.05.2026</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">06.05.-08.05.2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(Теоретический курс в дистанционном формате 06.05.-07.05.26; Очно в УЦ и экзамен 08.05.26)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">20.05.-21.05.2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(Теоретический курс в дистанционном формате 20.05.26; Практика в УЦ и экзамен 21.05.26)</t>
+    </r>
+  </si>
+  <si>
+    <t>25.05.-29.05.2026</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">25.05.-27.05.2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(Теоретический курс в дистанционном формате 25.05.-26.05.26; Практика в УЦ  27.05.26)</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF0A0A0A"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
     </font>
     <font>
       <b/>
@@ -118,6 +274,51 @@
       <family val="1"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -127,7 +328,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -135,14 +336,61 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -422,24 +670,134 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5526FC9-C698-47D0-99AD-2CAE6F6B4D6B}">
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="126.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="102.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.77734375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>0</v>
+    </row>
+    <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -448,164 +806,134 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E995CB2D-0483-4159-8CFD-45A6D8D13217}">
-  <dimension ref="A1:C4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09D15B49-DB73-470B-8414-12638B9BBD00}">
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="102.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" customWidth="1"/>
+    <col min="2" max="2" width="62.21875" customWidth="1"/>
+    <col min="3" max="3" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
+    </row>
+    <row r="3" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D759A286-A09C-403E-AC19-B252F9B7FCEC}">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="B7" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5526FC9-C698-47D0-99AD-2CAE6F6B4D6B}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="11" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>0</v>
+      <c r="B11" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/main/data/schedule.xlsx
+++ b/main/data/schedule.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\project\energetic_site\main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38A8D5C6-9EB0-4A3A-B10D-9570AF543F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68D6B593-C160-4B55-BEF6-40F24E06E44C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Апрель 2026" sheetId="4" r:id="rId1"/>
     <sheet name="Май 2026" sheetId="5" r:id="rId2"/>
+    <sheet name="Июнь 2026" sheetId="6" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="47">
   <si>
     <t>Название</t>
   </si>
@@ -62,9 +63,6 @@
   </si>
   <si>
     <t>Программа обучения по использованию (применению) средств индивидуальной защиты</t>
-  </si>
-  <si>
-    <t>Программа повышения квалификации для рабочих люльки, находящихся на подъемнике (вышке)</t>
   </si>
   <si>
     <t>Повышение квалификации в области пожарной безопасности</t>
@@ -244,6 +242,75 @@
         <charset val="204"/>
       </rPr>
       <t>(Теоретический курс в дистанционном формате 25.05.-26.05.26; Практика в УЦ  27.05.26)</t>
+    </r>
+  </si>
+  <si>
+    <t>01.06.-03.06.2026</t>
+  </si>
+  <si>
+    <t>04.06.-08.06.2026</t>
+  </si>
+  <si>
+    <t>15.06.-19.06.2026</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">22.06.-26.06.2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(Теоретический курс в дистанционном формате 22.06.-24.06.26; Практика в УЦ и экзамен 25.06.-26.06.26)</t>
+    </r>
+  </si>
+  <si>
+    <t>08.06.-10.06.2026</t>
+  </si>
+  <si>
+    <t>15.06.-25.06.2026</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">17.06.-18.06.2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(Теоретический курс в дистанционном формате 17.06.26; Практика в УЦ и экзамен 18.06.26)</t>
+    </r>
+  </si>
+  <si>
+    <t>Программа ПК персонала организаций, эксплуатирующих опасные производственные объекты, на которых используются сосуды, работающие под избыточным давлением</t>
+  </si>
+  <si>
+    <t>Программа повышения квалификации для электротехнического персонала</t>
+  </si>
+  <si>
+    <t>Программа повышения квалификации для рабочих люльки, находящихся на подъёмнике (вышке)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">24.06.-26.06.2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(Теоретический курс в дистанционном формате 24.06.-25.06.25; Практика в УЦ 26.06.26)</t>
     </r>
   </si>
 </sst>
@@ -368,7 +435,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -390,6 +457,18 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -695,10 +774,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -706,7 +785,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
         <v>3</v>
@@ -717,10 +796,10 @@
         <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -728,10 +807,10 @@
         <v>7</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -739,7 +818,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
         <v>3</v>
@@ -750,10 +829,10 @@
         <v>9</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -761,10 +840,10 @@
         <v>10</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -772,32 +851,32 @@
         <v>11</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -810,7 +889,7 @@
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" customWidth="1"/>
+    <col min="1" max="1" width="154" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="62.21875" customWidth="1"/>
     <col min="3" max="3" width="19" customWidth="1"/>
   </cols>
@@ -828,10 +907,10 @@
     </row>
     <row r="2" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
@@ -839,13 +918,13 @@
     </row>
     <row r="3" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -853,7 +932,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
         <v>3</v>
@@ -864,7 +943,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
         <v>3</v>
@@ -872,13 +951,13 @@
     </row>
     <row r="6" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
@@ -886,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -897,29 +976,29 @@
         <v>9</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
         <v>3</v>
@@ -927,13 +1006,137 @@
     </row>
     <row r="11" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59C48A80-9F65-490A-86C4-CC142AFB4D83}">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="58.5546875" customWidth="1"/>
+    <col min="3" max="3" width="28.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/main/data/schedule.xlsx
+++ b/main/data/schedule.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\project\energetic_site\main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68D6B593-C160-4B55-BEF6-40F24E06E44C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDEFFCB2-E41B-4B27-AAED-4DA6DC2C1B94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Апрель 2026" sheetId="4" r:id="rId1"/>
     <sheet name="Май 2026" sheetId="5" r:id="rId2"/>
     <sheet name="Июнь 2026" sheetId="6" r:id="rId3"/>
+    <sheet name="Июль 2026" sheetId="7" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="47">
   <si>
     <t>Название</t>
   </si>
@@ -1142,4 +1143,129 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF4D3C00-0015-4FF3-B1FB-006A6552A8C7}">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="63.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="62.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/main/data/schedule.xlsx
+++ b/main/data/schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\project\energetic_site\main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDEFFCB2-E41B-4B27-AAED-4DA6DC2C1B94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0031F7E0-8823-47ED-A8AB-14A96D53DA8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="56">
   <si>
     <t>Название</t>
   </si>
@@ -312,6 +312,57 @@
         <charset val="204"/>
       </rPr>
       <t>(Теоретический курс в дистанционном формате 24.06.-25.06.25; Практика в УЦ 26.06.26)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">06.07.-10.07.2026  </t>
+  </si>
+  <si>
+    <t>16.07.-22.07.2026</t>
+  </si>
+  <si>
+    <t>13.07.-23.07.2026</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">23.07.-24.07.2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(Теоретический курс в дистанционном формате 23.07.26; Практика в УЦ и экзамен 24.07.26)</t>
+    </r>
+  </si>
+  <si>
+    <t>Программа обучения по использованию (применению) средств индивидуальной защиты (СИЗ)</t>
+  </si>
+  <si>
+    <t>Программа обучения по оказанию первой помощи пострадавшим (ПП)</t>
+  </si>
+  <si>
+    <t>Программы обучения требованиям охраны труда (А, Б, В)</t>
+  </si>
+  <si>
+    <t>Программа повышения квалификации электротехнического персонала</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">29.07.-31.07.2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">(Теоретический курс в дистанционном формате 29.07.-31.07.26; Практика в УЦ 31.07.26) </t>
     </r>
   </si>
 </sst>
@@ -396,7 +447,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -432,11 +483,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -470,6 +536,19 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1147,7 +1226,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF4D3C00-0015-4FF3-B1FB-006A6552A8C7}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="63.33203125" bestFit="1" customWidth="1"/>
@@ -1155,113 +1234,91 @@
     <col min="3" max="3" width="28.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C2" t="s">
+    <row r="2" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="14" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="14" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" t="s">
+    <row r="5" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="14" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="11" t="s">
+    <row r="6" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="B8" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="14" t="s">
         <v>21</v>
       </c>
     </row>

--- a/main/data/schedule.xlsx
+++ b/main/data/schedule.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\project\energetic_site\main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0031F7E0-8823-47ED-A8AB-14A96D53DA8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F1DFA35-605C-42EA-810D-34C20BDD31E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Апрель 2026" sheetId="4" r:id="rId1"/>
     <sheet name="Май 2026" sheetId="5" r:id="rId2"/>
     <sheet name="Июнь 2026" sheetId="6" r:id="rId3"/>
     <sheet name="Июль 2026" sheetId="7" r:id="rId4"/>
+    <sheet name="Август 2026" sheetId="8" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="65">
   <si>
     <t>Название</t>
   </si>
@@ -364,6 +365,81 @@
       </rPr>
       <t xml:space="preserve">(Теоретический курс в дистанционном формате 29.07.-31.07.26; Практика в УЦ 31.07.26) </t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">10.08.-14.08.2026        </t>
+  </si>
+  <si>
+    <t>10.08-20.08.2026</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">12.08.-13.08.2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(Теоретический курс в дистанционном формате 12.08.26; Практика в УЦ и экзамен 13.08.26)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">13.08.-14.08.2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(Теоретический курс в дистанционном формате 13.08.26; Практика в УЦ и экзамен 14.08.26)</t>
+    </r>
+  </si>
+  <si>
+    <t>13.08.-20.08.2026</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">17.08.-29.09.2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(Теоретический курс в дистанционном формате 17.08.-25.09.26; Практика в УЦ  28.09.-29.09.26)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">26.08.-28.08.2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(Теоретический курс в дистанционном формате 26.08.-27.08.26; Практика в УЦ  28.08.26)</t>
+    </r>
+  </si>
+  <si>
+    <t>Предаттестационная подготовка лиц, ответственных за исправное состояние и безопасную эксплуатацию тепловых энергоустановок</t>
+  </si>
+  <si>
+    <t>Специалист по пожарной профилактике</t>
   </si>
 </sst>
 </file>
@@ -502,7 +578,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -549,6 +625,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1325,4 +1404,116 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91630F25-34E5-46E8-B21D-78EE53099922}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="3" width="51.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/main/data/schedule.xlsx
+++ b/main/data/schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\project\energetic_site\main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F1DFA35-605C-42EA-810D-34C20BDD31E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6023A73E-FF7E-46A3-A1F3-824F3B8C9645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="67">
   <si>
     <t>Название</t>
   </si>
@@ -440,6 +440,12 @@
   </si>
   <si>
     <t>Специалист по пожарной профилактике</t>
+  </si>
+  <si>
+    <t>Программа повышения квалификации для рабочих люльки, находящихся на подъемнике (вышке)</t>
+  </si>
+  <si>
+    <t>24.08.-26.08.2026</t>
   </si>
 </sst>
 </file>
@@ -523,7 +529,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -574,11 +580,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -627,6 +644,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1408,7 +1428,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91630F25-34E5-46E8-B21D-78EE53099922}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="51.77734375" customWidth="1"/>
@@ -1502,14 +1522,25 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="11" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B10" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C10" s="14" t="s">
         <v>21</v>
       </c>
     </row>

--- a/main/data/schedule.xlsx
+++ b/main/data/schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\project\energetic_site\main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6023A73E-FF7E-46A3-A1F3-824F3B8C9645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{518458B1-F25B-45FB-B8B4-1E5562089412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Апрель 2026" sheetId="4" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Июнь 2026" sheetId="6" r:id="rId3"/>
     <sheet name="Июль 2026" sheetId="7" r:id="rId4"/>
     <sheet name="Август 2026" sheetId="8" r:id="rId5"/>
+    <sheet name="Сентябрь" sheetId="9" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="79">
   <si>
     <t>Название</t>
   </si>
@@ -446,6 +447,102 @@
   </si>
   <si>
     <t>24.08.-26.08.2026</t>
+  </si>
+  <si>
+    <t>07.09.-09.09. 2026</t>
+  </si>
+  <si>
+    <t>14.09.-24.09. 2026</t>
+  </si>
+  <si>
+    <t>14.09.-18.09. 2026</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">16.09.-07.10.2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> (Теоретический курс в дистанционном формате16.09.-18.09.; Производственное обучение на рабочих местах 21.09.-02.10.26, Теоретический курс и Практика в УЦ очный формат 05.10.-06.10.26, КЭ 07.10.2026)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">17.09.-23.09.2026 </t>
+  </si>
+  <si>
+    <r>
+      <t>17.09.-18.09.2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(Теоретический курс в дистанционном формате 17.09.26; Практика в УЦ и экзамен 18.09.26)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>21.09.-22.09.2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(Теоретический курс в дистанционном формате 21.09.26; Практика в УЦ и экзамен 22.09.26)</t>
+    </r>
+  </si>
+  <si>
+    <t>23.09.-25.09.2026</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">23.09.-29.09.2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(Теоретический курс в дистанционном формате 23.09.-25.09.26; Практика в УЦ и экзамен 28.09.-29.09.26)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">23.09.-25.09.2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(Теоретический курс в дистанционном формате 23.09.-24.09.26 Практика в УЦ 25.09.26)</t>
+    </r>
+  </si>
+  <si>
+    <t>Стропальщик</t>
+  </si>
+  <si>
+    <t>Повышение квалификации для рабочих по управлению подъемными сооружениями грузоподъемностью до 10 тонн включительно, управляемыми с пола</t>
   </si>
 </sst>
 </file>
@@ -595,7 +692,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -646,7 +743,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1547,4 +1647,146 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A5EE2A0-C40B-43DD-8D78-AF33EAB09449}">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="3" width="51.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/main/data/schedule.xlsx
+++ b/main/data/schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\project\energetic_site\main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{518458B1-F25B-45FB-B8B4-1E5562089412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5437497D-AE35-4D11-B344-A3E56FBE0013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Июнь 2026" sheetId="6" r:id="rId3"/>
     <sheet name="Июль 2026" sheetId="7" r:id="rId4"/>
     <sheet name="Август 2026" sheetId="8" r:id="rId5"/>
-    <sheet name="Сентябрь" sheetId="9" r:id="rId6"/>
+    <sheet name="Сентябрь 2026" sheetId="9" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="91">
   <si>
     <t>Название</t>
   </si>
@@ -452,12 +452,6 @@
     <t>07.09.-09.09. 2026</t>
   </si>
   <si>
-    <t>14.09.-24.09. 2026</t>
-  </si>
-  <si>
-    <t>14.09.-18.09. 2026</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">16.09.-07.10.2026 </t>
     </r>
@@ -543,6 +537,48 @@
   </si>
   <si>
     <t>Повышение квалификации для рабочих по управлению подъемными сооружениями грузоподъемностью до 10 тонн включительно, управляемыми с пола</t>
+  </si>
+  <si>
+    <t>Машинист (кочегар) котельной</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07.09.-16.10.2026 (Теоретический курс в очном формате 07.09.-11.09.26, Теоретический курс в дистанционном формате  14.09.- 23.09.26, Производственное обучение на рабочих местах 24.09.-14.10., КЭ15.10-16.10.) </t>
+  </si>
+  <si>
+    <t>09.09-15.09.2026 (Теоретический курс в дистанционном формате 09.09.-11.09.26; Практика в УЦ и экзамен 14.09.-15.09.26)</t>
+  </si>
+  <si>
+    <t>Повышение квалификации электротехнического персонала (правила безопасной эксплуатации бензоинструмента)</t>
+  </si>
+  <si>
+    <t>09.09.-11.09.2026</t>
+  </si>
+  <si>
+    <t>Электромонтер по эксплуатации распределительных сетей</t>
+  </si>
+  <si>
+    <t>11.09-17.09.2026 (Теоретический курс в дистанционном формате 11.09.-15.09.26; Практика в УЦ и экзамен 16.09.-17.09.26)</t>
+  </si>
+  <si>
+    <t>14.09-23.10.2026 (Теоретический курс в дистанционном формате 14.09.-21.09.26, Производственное обучение на рабочих местах 22.09.-12.10.26,Теоретический курс и Практика в УЦ очный формат 13.10.-21.10.26, КЭ 22.10.-23.10.26)</t>
+  </si>
+  <si>
+    <t>21.09.-25.09.2026 (Теоретический курс в дистанционном формате 21.09.-23.09.26; Практика в УЦ и экзамен 24.09.-25.09.26)</t>
+  </si>
+  <si>
+    <t>Электромонтер оперативно-выездной бригады</t>
+  </si>
+  <si>
+    <t>Электромонтер по обслуживанию подстанций</t>
+  </si>
+  <si>
+    <t>21.09-30.10.2026 (Теоретический курс в дистанционном формате 21.09.-28.09.26, Производственное обучение на рабочих местах 29.10.-19.10.26,Теоретический курс и Практика в УЦ очный формат 20.10.-28.10.26, КЭ 29.10.-30.10.26)</t>
+  </si>
+  <si>
+    <t>14.09.-24.09.2026</t>
+  </si>
+  <si>
+    <t>14.09.-18.09.2026</t>
   </si>
 </sst>
 </file>
@@ -692,7 +728,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -746,8 +782,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1651,13 +1694,13 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A5EE2A0-C40B-43DD-8D78-AF33EAB09449}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="51.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -1668,121 +1711,212 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="21" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B3" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C3" s="14" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="12" t="s">
+    <row r="4" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B6" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+      <c r="A10" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+      <c r="A12" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="B12" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="C3" s="14" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="8" t="s">
+      <c r="C12" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="14" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="B6" s="8" t="s">
+      <c r="C13" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="16" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="8" t="s">
+      <c r="C14" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="14" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="8" t="s">
+      <c r="C15" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+      <c r="A16" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+      <c r="A17" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="8" t="s">
+      <c r="C18" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="B10" s="8" t="s">
+      <c r="C19" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A20" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="C10" s="14" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" s="14" t="s">
+      <c r="C20" s="14" t="s">
         <v>21</v>
       </c>
     </row>

--- a/main/data/schedule.xlsx
+++ b/main/data/schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\project\energetic_site\main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5437497D-AE35-4D11-B344-A3E56FBE0013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4D56196-3DE1-4C76-83B0-F5D2B89F88C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1711,92 +1711,92 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+    <row r="2" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B3" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="23" t="s">
-        <v>65</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>67</v>
-      </c>
       <c r="C3" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="14" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="23" t="s">
+    <row r="5" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B5" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="C4" s="14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="23" t="s">
-        <v>80</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>81</v>
-      </c>
       <c r="C5" s="14" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="23" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B8" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C6" s="14" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="23" t="s">
+      <c r="C8" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B9" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C7" s="14" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>83</v>
-      </c>
       <c r="C9" s="14" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="66" x14ac:dyDescent="0.3">
@@ -1810,23 +1810,23 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="66" x14ac:dyDescent="0.3">
       <c r="A11" s="21" t="s">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="66" x14ac:dyDescent="0.3">
-      <c r="A12" s="21" t="s">
-        <v>75</v>
+    <row r="12" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="24" t="s">
+        <v>11</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C12" s="14" t="s">
         <v>21</v>
@@ -1845,21 +1845,21 @@
     </row>
     <row r="14" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A14" s="24" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C14" s="14" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="24" t="s">
-        <v>25</v>
+    <row r="15" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="21" t="s">
+        <v>4</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>21</v>
@@ -1898,23 +1898,23 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A19" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B20" s="15" t="s">
         <v>73</v>
-      </c>
-      <c r="C19" s="14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>74</v>
       </c>
       <c r="C20" s="14" t="s">
         <v>21</v>
